--- a/drivers/xlsx/testdata/sakila_subset.xlsx
+++ b/drivers/xlsx/testdata/sakila_subset.xlsx
@@ -878,7 +878,7 @@
     <t>ACADEMY DINOSAUR</t>
   </si>
   <si>
-    <t>An Epic Drama of a Feminist And a Mad Scientist who must Battle a Teacher in The Canadian Rockies</t>
+    <t>A Epic Drama of a Feminist And a Mad Scientist who must Battle a Teacher in The Canadian Rockies</t>
   </si>
   <si>
     <t>2006</t>
@@ -950,7 +950,7 @@
     <t>AIRPORT POLLOCK</t>
   </si>
   <si>
-    <t>An Epic Tale of a Moose And a Girl who must Confront a Monkey in Ancient India</t>
+    <t>A Epic Tale of a Moose And a Girl who must Confront a Monkey in Ancient India</t>
   </si>
   <si>
     <t>R</t>
@@ -1109,7 +1109,7 @@
     <t>ANYTHING SAVANNAH</t>
   </si>
   <si>
-    <t>An Epic Story of a Pastry Chef And a Woman who must Chase a Feminist in An Abandoned Fun House</t>
+    <t>A Epic Story of a Pastry Chef And a Woman who must Chase a Feminist in An Abandoned Fun House</t>
   </si>
   <si>
     <t>APACHE DIVINE</t>
@@ -1256,7 +1256,7 @@
     <t>BANG KWAI</t>
   </si>
   <si>
-    <t>An Epic Drama of a Madman And a Cat who must Face a A Shark in An Abandoned Amusement Park</t>
+    <t>A Epic Drama of a Madman And a Cat who must Face a A Shark in An Abandoned Amusement Park</t>
   </si>
   <si>
     <t>BANGER PINOCCHIO</t>
@@ -1322,7 +1322,7 @@
     <t>BEETHOVEN EXORCIST</t>
   </si>
   <si>
-    <t>An Epic Display of a Pioneer And a Student who must Challenge a Butler in The Gulf of Mexico</t>
+    <t>A Epic Display of a Pioneer And a Student who must Challenge a Butler in The Gulf of Mexico</t>
   </si>
   <si>
     <t>BEHAVIOR RUNAWAY</t>
@@ -1520,7 +1520,7 @@
     <t>BRIDE INTRIGUE</t>
   </si>
   <si>
-    <t>An Epic Tale of a Robot And a Monkey who must Vanquish a Man in New Orleans</t>
+    <t>A Epic Tale of a Robot And a Monkey who must Vanquish a Man in New Orleans</t>
   </si>
   <si>
     <t>BRIGHT ENCOUNTERS</t>
@@ -1808,7 +1808,7 @@
     <t>CHISUM BEHAVIOR</t>
   </si>
   <si>
-    <t>An Epic Documentary of a Sumo Wrestler And a Butler who must Kill a Car in Ancient India</t>
+    <t>A Epic Documentary of a Sumo Wrestler And a Butler who must Kill a Car in Ancient India</t>
   </si>
   <si>
     <t>CHITTY LOCK</t>
@@ -1898,7 +1898,7 @@
     <t>CLUB GRAFFITI</t>
   </si>
   <si>
-    <t>An Epic Tale of a Pioneer And a Hunter who must Escape a Girl in A U-Boat</t>
+    <t>A Epic Tale of a Pioneer And a Hunter who must Escape a Girl in A U-Boat</t>
   </si>
   <si>
     <t>CLUE GRAIL</t>
@@ -2150,7 +2150,7 @@
     <t>DADDY PITTSBURGH</t>
   </si>
   <si>
-    <t>An Epic Story of a A Shark And a Student who must Confront a Explorer in The Gulf of Mexico</t>
+    <t>A Epic Story of a A Shark And a Student who must Confront a Explorer in The Gulf of Mexico</t>
   </si>
   <si>
     <t>DAISY MENAGERIE</t>
@@ -2282,7 +2282,7 @@
     <t>DESPERATE TRAINSPOTTING</t>
   </si>
   <si>
-    <t>An Epic Yarn of a Forensic Psychologist And a Teacher who must Face a Lumberjack in California</t>
+    <t>A Epic Yarn of a Forensic Psychologist And a Teacher who must Face a Lumberjack in California</t>
   </si>
   <si>
     <t>DESTINATION JERK</t>
@@ -2300,7 +2300,7 @@
     <t>DETAILS PACKER</t>
   </si>
   <si>
-    <t>An Epic Saga of a Waitress And a Composer who must Face a Boat in A U-Boat</t>
+    <t>A Epic Saga of a Waitress And a Composer who must Face a Boat in A U-Boat</t>
   </si>
   <si>
     <t>DETECTIVE VISION</t>
@@ -2450,13 +2450,13 @@
     <t>DREAM PICKUP</t>
   </si>
   <si>
-    <t>An Epic Display of a Car And a Composer who must Overcome a Forensic Psychologist in The Gulf of Mexico</t>
+    <t>A Epic Display of a Car And a Composer who must Overcome a Forensic Psychologist in The Gulf of Mexico</t>
   </si>
   <si>
     <t>DRIFTER COMMANDMENTS</t>
   </si>
   <si>
-    <t>An Epic Reflection of a Womanizer And a Squirrel who must Discover a Husband in A Jet Boat</t>
+    <t>A Epic Reflection of a Womanizer And a Squirrel who must Discover a Husband in A Jet Boat</t>
   </si>
   <si>
     <t>DRIVER ANNIE</t>
@@ -2486,7 +2486,7 @@
     <t>DRUMS DYNAMITE</t>
   </si>
   <si>
-    <t>An Epic Display of a Crocodile And a Crocodile who must Confront a Dog in An Abandoned Amusement Park</t>
+    <t>A Epic Display of a Crocodile And a Crocodile who must Confront a Dog in An Abandoned Amusement Park</t>
   </si>
   <si>
     <t>DUCK RACER</t>
@@ -2744,7 +2744,7 @@
     <t>FAMILY SWEET</t>
   </si>
   <si>
-    <t>An Epic Documentary of a Teacher And a Boy who must Escape a Woman in Berlin</t>
+    <t>A Epic Documentary of a Teacher And a Boy who must Escape a Woman in Berlin</t>
   </si>
   <si>
     <t>FANTASIA PARK</t>
@@ -3164,7 +3164,7 @@
     <t>GOSFORD DONNIE</t>
   </si>
   <si>
-    <t>An Epic Panorama of a Mad Scientist And a Monkey who must Redeem a Secret Agent in Berlin</t>
+    <t>A Epic Panorama of a Mad Scientist And a Monkey who must Redeem a Secret Agent in Berlin</t>
   </si>
   <si>
     <t>GRACELAND DYNAMITE</t>
@@ -3242,7 +3242,7 @@
     <t>GROSSE WONDERFUL</t>
   </si>
   <si>
-    <t>An Epic Drama of a Cat And a Explorer who must Redeem a Moose in Australia</t>
+    <t>A Epic Drama of a Cat And a Explorer who must Redeem a Moose in Australia</t>
   </si>
   <si>
     <t>GROUNDHOG UNCUT</t>
@@ -3266,7 +3266,7 @@
     <t>GUNFIGHT MOON</t>
   </si>
   <si>
-    <t>An Epic Reflection of a Pastry Chef And a Explorer who must Reach a Dentist in The Sahara Desert</t>
+    <t>A Epic Reflection of a Pastry Chef And a Explorer who must Reach a Dentist in The Sahara Desert</t>
   </si>
   <si>
     <t>GUNFIGHTER MUSSOLINI</t>
@@ -3284,7 +3284,7 @@
     <t>HALF OUTFIELD</t>
   </si>
   <si>
-    <t>An Epic Epistle of a Database Administrator And a Crocodile who must Face a Madman in A Jet Boat</t>
+    <t>A Epic Epistle of a Database Administrator And a Crocodile who must Face a Madman in A Jet Boat</t>
   </si>
   <si>
     <t>HALL CASSIDY</t>
@@ -3440,7 +3440,7 @@
     <t>HILLS NEIGHBORS</t>
   </si>
   <si>
-    <t>An Epic Display of a Hunter And a Feminist who must Sink a Car in A U-Boat</t>
+    <t>A Epic Display of a Hunter And a Feminist who must Sink a Car in A U-Boat</t>
   </si>
   <si>
     <t>HOBBIT ALIEN</t>
@@ -3644,7 +3644,7 @@
     <t>IGBY MAKER</t>
   </si>
   <si>
-    <t>An Epic Documentary of a Hunter And a Dog who must Outgun a Dog in A Baloon Factory</t>
+    <t>A Epic Documentary of a Hunter And a Dog who must Outgun a Dog in A Baloon Factory</t>
   </si>
   <si>
     <t>ILLUSION AMELIE</t>
@@ -3662,7 +3662,7 @@
     <t>IMPACT ALADDIN</t>
   </si>
   <si>
-    <t>An Epic Character Study of a Frisbee And a Moose who must Outgun a Technical Writer in A Shark Tank</t>
+    <t>A Epic Character Study of a Frisbee And a Moose who must Outgun a Technical Writer in A Shark Tank</t>
   </si>
   <si>
     <t>IMPOSSIBLE PREJUDICE</t>
@@ -3704,7 +3704,7 @@
     <t>INSECTS STONE</t>
   </si>
   <si>
-    <t>An Epic Display of a Butler And a Dog who must Vanquish a Crocodile in A Manhattan Penthouse</t>
+    <t>A Epic Display of a Butler And a Dog who must Vanquish a Crocodile in A Manhattan Penthouse</t>
   </si>
   <si>
     <t>INSIDER ARIZONA</t>
@@ -3860,7 +3860,7 @@
     <t>JINGLE SAGEBRUSH</t>
   </si>
   <si>
-    <t>An Epic Character Study of a Feminist And a Student who must Meet a Woman in A Baloon</t>
+    <t>A Epic Character Study of a Feminist And a Student who must Meet a Woman in A Baloon</t>
   </si>
   <si>
     <t>JOON NORTHWEST</t>
@@ -3872,7 +3872,7 @@
     <t>JUGGLER HARDLY</t>
   </si>
   <si>
-    <t>An Epic Story of a Mad Cow And a Astronaut who must Challenge a Car in California</t>
+    <t>A Epic Story of a Mad Cow And a Astronaut who must Challenge a Car in California</t>
   </si>
   <si>
     <t>JUMANJI BLADE</t>
@@ -3896,7 +3896,7 @@
     <t>KANE EXORCIST</t>
   </si>
   <si>
-    <t>An Epic Documentary of a Composer And a Robot who must Overcome a Car in Berlin</t>
+    <t>A Epic Documentary of a Composer And a Robot who must Overcome a Car in Berlin</t>
   </si>
   <si>
     <t>KARATE MOON</t>
@@ -3992,7 +3992,7 @@
     <t>LANGUAGE COWBOY</t>
   </si>
   <si>
-    <t>An Epic Yarn of a Cat And a Madman who must Vanquish a Dentist in An Abandoned Amusement Park</t>
+    <t>A Epic Yarn of a Cat And a Madman who must Vanquish a Dentist in An Abandoned Amusement Park</t>
   </si>
   <si>
     <t>LAWLESS VISION</t>
@@ -4520,7 +4520,7 @@
     <t>MOONWALKER FOOL</t>
   </si>
   <si>
-    <t>An Epic Drama of a Feminist And a Pioneer who must Sink a Composer in New Orleans</t>
+    <t>A Epic Drama of a Feminist And a Pioneer who must Sink a Composer in New Orleans</t>
   </si>
   <si>
     <t>MOSQUITO ARMAGEDDON</t>
@@ -4616,7 +4616,7 @@
     <t>MYSTIC TRUMAN</t>
   </si>
   <si>
-    <t>An Epic Yarn of a Teacher And a Hunter who must Outgun a Explorer in Soviet Georgia</t>
+    <t>A Epic Yarn of a Teacher And a Hunter who must Outgun a Explorer in Soviet Georgia</t>
   </si>
   <si>
     <t>NAME DETECTIVE</t>
@@ -4628,7 +4628,7 @@
     <t>NASH CHOCOLAT</t>
   </si>
   <si>
-    <t>An Epic Reflection of a Monkey And a Mad Cow who must Kill a Forensic Psychologist in An Abandoned Mine Shaft</t>
+    <t>A Epic Reflection of a Monkey And a Mad Cow who must Kill a Forensic Psychologist in An Abandoned Mine Shaft</t>
   </si>
   <si>
     <t>NATIONAL STORY</t>
@@ -4832,7 +4832,7 @@
     <t>OZ LIAISONS</t>
   </si>
   <si>
-    <t>An Epic Yarn of a Mad Scientist And a Cat who must Confront a Womanizer in A Baloon Factory</t>
+    <t>A Epic Yarn of a Mad Scientist And a Cat who must Confront a Womanizer in A Baloon Factory</t>
   </si>
   <si>
     <t>PACIFIC AMISTAD</t>
@@ -4844,7 +4844,7 @@
     <t>PACKER MADIGAN</t>
   </si>
   <si>
-    <t>An Epic Display of a Sumo Wrestler And a Forensic Psychologist who must Build a Woman in An Abandoned Amusement Park</t>
+    <t>A Epic Display of a Sumo Wrestler And a Forensic Psychologist who must Build a Woman in An Abandoned Amusement Park</t>
   </si>
   <si>
     <t>PAJAMA JAWBREAKER</t>
@@ -4958,7 +4958,7 @@
     <t>PELICAN COMFORTS</t>
   </si>
   <si>
-    <t>An Epic Documentary of a Boy And a Monkey who must Pursue a Astronaut in Berlin</t>
+    <t>A Epic Documentary of a Boy And a Monkey who must Pursue a Astronaut in Berlin</t>
   </si>
   <si>
     <t>PERDITION FARGO</t>
@@ -4976,7 +4976,7 @@
     <t>PERSONAL LADYBUGS</t>
   </si>
   <si>
-    <t>An Epic Saga of a Hunter And a Technical Writer who must Conquer a Cat in Ancient Japan</t>
+    <t>A Epic Saga of a Hunter And a Technical Writer who must Conquer a Cat in Ancient Japan</t>
   </si>
   <si>
     <t>PET HAUNTING</t>
@@ -5042,7 +5042,7 @@
     <t>PIZZA JUMANJI</t>
   </si>
   <si>
-    <t>An Epic Saga of a Cat And a Squirrel who must Outgun a Robot in A U-Boat</t>
+    <t>A Epic Saga of a Cat And a Squirrel who must Outgun a Robot in A U-Boat</t>
   </si>
   <si>
     <t>PLATOON INSTINCT</t>
@@ -5102,7 +5102,7 @@
     <t>PREJUDICE OLEANDER</t>
   </si>
   <si>
-    <t>An Epic Saga of a Boy And a Dentist who must Outrace a Madman in A U-Boat</t>
+    <t>A Epic Saga of a Boy And a Dentist who must Outrace a Madman in A U-Boat</t>
   </si>
   <si>
     <t>PRESIDENT BANG</t>
@@ -5300,7 +5300,7 @@
     <t>RESURRECTION SILVERADO</t>
   </si>
   <si>
-    <t>An Epic Yarn of a Robot And a Explorer who must Challenge a Girl in A MySQL Convention</t>
+    <t>A Epic Yarn of a Robot And a Explorer who must Challenge a Girl in A MySQL Convention</t>
   </si>
   <si>
     <t>REUNION WITCHES</t>
@@ -5738,7 +5738,7 @@
     <t>SINNERS ATLANTIS</t>
   </si>
   <si>
-    <t>An Epic Display of a Dog And a Boat who must Succumb a Mad Scientist in An Abandoned Mine Shaft</t>
+    <t>A Epic Display of a Dog And a Boat who must Succumb a Mad Scientist in An Abandoned Mine Shaft</t>
   </si>
   <si>
     <t>SISTER FREDDY</t>
@@ -5750,7 +5750,7 @@
     <t>SKY MIRACLE</t>
   </si>
   <si>
-    <t>An Epic Drama of a Mad Scientist And a Explorer who must Succumb a Waitress in An Abandoned Fun House</t>
+    <t>A Epic Drama of a Mad Scientist And a Explorer who must Succumb a Waitress in An Abandoned Fun House</t>
   </si>
   <si>
     <t>SLACKER LIAISONS</t>
@@ -6122,7 +6122,7 @@
     <t>SUNDANCE INVASION</t>
   </si>
   <si>
-    <t>An Epic Drama of a Lumberjack And a Explorer who must Confront a Hunter in A Baloon Factory</t>
+    <t>A Epic Drama of a Lumberjack And a Explorer who must Confront a Hunter in A Baloon Factory</t>
   </si>
   <si>
     <t>SUNRISE LEAGUE</t>
@@ -6536,7 +6536,7 @@
     <t>VAMPIRE WHALE</t>
   </si>
   <si>
-    <t>An Epic Story of a Lumberjack And a Monkey who must Confront a Pioneer in A MySQL Convention</t>
+    <t>A Epic Story of a Lumberjack And a Monkey who must Confront a Pioneer in A MySQL Convention</t>
   </si>
   <si>
     <t>VANILLA DAY</t>
@@ -6644,7 +6644,7 @@
     <t>VOYAGE LEGALLY</t>
   </si>
   <si>
-    <t>An Epic Tale of a Squirrel And a Hunter who must Conquer a Boy in An Abandoned Mine Shaft</t>
+    <t>A Epic Tale of a Squirrel And a Hunter who must Conquer a Boy in An Abandoned Mine Shaft</t>
   </si>
   <si>
     <t>WAGON JAWS</t>
